--- a/output_boron/boron_Intermediate_foster_2008.xlsx
+++ b/output_boron/boron_Intermediate_foster_2008.xlsx
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">10.1016/j.epsl.2008.04.015</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_foster_2008.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_foster_2008_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1402,7 +1402,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1462,12 +1462,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1581,7 +1575,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1663,7 +1657,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2270,7 +2263,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2347,7 +2340,7 @@
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2424,7 +2417,7 @@
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2501,7 +2494,7 @@
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2578,7 +2571,7 @@
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2655,7 +2648,7 @@
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -2732,7 +2725,7 @@
       <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" t="s">
         <v>242</v>
       </c>
       <c r="D11" t="s">
@@ -2809,7 +2802,7 @@
       <c r="B12" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" t="s">
         <v>242</v>
       </c>
       <c r="D12" t="s">
@@ -2886,7 +2879,7 @@
       <c r="B13" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" t="s">
         <v>242</v>
       </c>
       <c r="D13" t="s">
@@ -2963,7 +2956,7 @@
       <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" t="s">
         <v>242</v>
       </c>
       <c r="D14" t="s">
@@ -3040,7 +3033,7 @@
       <c r="B15" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" t="s">
         <v>242</v>
       </c>
       <c r="D15" t="s">
@@ -3117,7 +3110,7 @@
       <c r="B16" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" t="s">
         <v>242</v>
       </c>
       <c r="D16" t="s">
@@ -3194,7 +3187,7 @@
       <c r="B17" t="s">
         <v>241</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" t="s">
         <v>242</v>
       </c>
       <c r="D17" t="s">
@@ -3271,7 +3264,7 @@
       <c r="B18" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" t="s">
         <v>242</v>
       </c>
       <c r="D18" t="s">
@@ -3348,7 +3341,7 @@
       <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" t="s">
         <v>242</v>
       </c>
       <c r="D19" t="s">
@@ -3425,7 +3418,7 @@
       <c r="B20" t="s">
         <v>241</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" t="s">
         <v>242</v>
       </c>
       <c r="D20" t="s">
@@ -3502,7 +3495,7 @@
       <c r="B21" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" t="s">
         <v>242</v>
       </c>
       <c r="D21" t="s">
@@ -3579,7 +3572,7 @@
       <c r="B22" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" t="s">
         <v>242</v>
       </c>
       <c r="D22" t="s">
@@ -3656,7 +3649,7 @@
       <c r="B23" t="s">
         <v>241</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" t="s">
         <v>242</v>
       </c>
       <c r="D23" t="s">
@@ -3733,7 +3726,7 @@
       <c r="B24" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" t="s">
         <v>242</v>
       </c>
       <c r="D24" t="s">
@@ -3810,7 +3803,7 @@
       <c r="B25" t="s">
         <v>241</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" t="s">
         <v>242</v>
       </c>
       <c r="D25" t="s">
@@ -3887,7 +3880,7 @@
       <c r="B26" t="s">
         <v>241</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" t="s">
         <v>242</v>
       </c>
       <c r="D26" t="s">
@@ -3964,7 +3957,7 @@
       <c r="B27" t="s">
         <v>241</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" t="s">
         <v>242</v>
       </c>
       <c r="D27" t="s">
@@ -4041,7 +4034,7 @@
       <c r="B28" t="s">
         <v>241</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" t="s">
         <v>242</v>
       </c>
       <c r="D28" t="s">
@@ -4118,7 +4111,7 @@
       <c r="B29" t="s">
         <v>241</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" t="s">
         <v>242</v>
       </c>
       <c r="D29" t="s">
@@ -4195,7 +4188,7 @@
       <c r="B30" t="s">
         <v>241</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" t="s">
         <v>242</v>
       </c>
       <c r="D30" t="s">
@@ -4272,7 +4265,7 @@
       <c r="B31" t="s">
         <v>241</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" t="s">
         <v>242</v>
       </c>
       <c r="D31" t="s">
@@ -4349,7 +4342,7 @@
       <c r="B32" t="s">
         <v>241</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" t="s">
         <v>242</v>
       </c>
       <c r="D32" t="s">
@@ -4426,7 +4419,7 @@
       <c r="B33" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" t="s">
         <v>242</v>
       </c>
       <c r="D33" t="s">
@@ -4503,7 +4496,7 @@
       <c r="B34" t="s">
         <v>241</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" t="s">
         <v>242</v>
       </c>
       <c r="D34" t="s">
@@ -4580,7 +4573,7 @@
       <c r="B35" t="s">
         <v>241</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" t="s">
         <v>242</v>
       </c>
       <c r="D35" t="s">
@@ -4657,7 +4650,7 @@
       <c r="B36" t="s">
         <v>241</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" t="s">
         <v>242</v>
       </c>
       <c r="D36" t="s">
@@ -4943,40 +4936,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
